--- a/data/trans_orig/P57_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161381</t>
+          <t>161837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202514</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152848</t>
+          <t>151237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191357</t>
+          <t>191124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325744</t>
+          <t>324829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381072</t>
+          <t>379707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216949</t>
+          <t>218199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258082</t>
+          <t>257626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201388</t>
+          <t>201621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239897</t>
+          <t>241508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431136</t>
+          <t>432501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486464</t>
+          <t>487379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172934</t>
+          <t>173253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>217698</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176171</t>
+          <t>176075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220571</t>
+          <t>221153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361884</t>
+          <t>359080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>422387</t>
+          <t>424800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365128</t>
+          <t>368257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413021</t>
+          <t>412702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338517</t>
+          <t>337935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382917</t>
+          <t>383013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722656</t>
+          <t>720243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783159</t>
+          <t>785963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200634</t>
+          <t>200080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>247360</t>
+          <t>250165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177735</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226909</t>
+          <t>225097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392787</t>
+          <t>390688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461539</t>
+          <t>457714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418925</t>
+          <t>416120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465651</t>
+          <t>466205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433543</t>
+          <t>435355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482717</t>
+          <t>480581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>865197</t>
+          <t>869022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933949</t>
+          <t>936048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148787</t>
+          <t>148353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196472</t>
+          <t>196035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124418</t>
+          <t>123018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169248</t>
+          <t>166085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286035</t>
+          <t>285461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349322</t>
+          <t>351215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>446328</t>
+          <t>446765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494013</t>
+          <t>494447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>476518</t>
+          <t>479681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521348</t>
+          <t>522748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>939244</t>
+          <t>937351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1002531</t>
+          <t>1003105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>104491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142554</t>
+          <t>143422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81421</t>
+          <t>79911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119547</t>
+          <t>120800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194992</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251238</t>
+          <t>253387</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334300</t>
+          <t>333432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>373227</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376256</t>
+          <t>375003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>414382</t>
+          <t>415892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>721419</t>
+          <t>719270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>777665</t>
+          <t>776529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66952</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99205</t>
+          <t>96572</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80207</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123731</t>
+          <t>122954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168433</t>
+          <t>167166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233173</t>
+          <t>235806</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265426</t>
+          <t>265751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297555</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329977</t>
+          <t>327967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541707</t>
+          <t>542974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586409</t>
+          <t>587186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59453</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36746</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68304</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>122318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197545</t>
+          <t>196563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219904</t>
+          <t>219172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328184</t>
+          <t>328555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359742</t>
+          <t>359898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>532275</t>
+          <t>531168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>572261</t>
+          <t>571313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>977133</t>
+          <t>977737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1087918</t>
+          <t>1087075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>877663</t>
+          <t>877838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>981482</t>
+          <t>976656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1875864</t>
+          <t>1880581</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2028846</t>
+          <t>2033723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2292815</t>
+          <t>2293658</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2403600</t>
+          <t>2402996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2546622</t>
+          <t>2551448</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2650441</t>
+          <t>2650266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4879991</t>
+          <t>4875114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5032973</t>
+          <t>5028256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>234536</t>
+          <t>233030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298238</t>
+          <t>297304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>162186</t>
+          <t>162212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207538</t>
+          <t>207422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413329</t>
+          <t>412423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490997</t>
+          <t>492551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101749</t>
+          <t>102683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165451</t>
+          <t>166957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105662</t>
+          <t>105778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151014</t>
+          <t>150988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222190</t>
+          <t>220636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>299858</t>
+          <t>300764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>199506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253751</t>
+          <t>250534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153471</t>
+          <t>144280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>285709</t>
+          <t>286686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>348449</t>
+          <t>340649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>519241</t>
+          <t>517867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169796</t>
+          <t>173013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224455</t>
+          <t>224041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224856</t>
+          <t>223879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357094</t>
+          <t>366285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414871</t>
+          <t>416245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>585663</t>
+          <t>593463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258196</t>
+          <t>256654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305821</t>
+          <t>306048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257069</t>
+          <t>259205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295146</t>
+          <t>295379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>530494</t>
+          <t>529826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589436</t>
+          <t>592379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230517</t>
+          <t>230290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278142</t>
+          <t>279684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246619</t>
+          <t>246386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284696</t>
+          <t>282560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488667</t>
+          <t>485724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547609</t>
+          <t>548277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>395597</t>
+          <t>393604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>733669</t>
+          <t>740368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225498</t>
+          <t>224137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287965</t>
+          <t>289858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>648755</t>
+          <t>644694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1133095</t>
+          <t>1112681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154117</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492189</t>
+          <t>494182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>419083</t>
+          <t>417190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481550</t>
+          <t>482911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>461739</t>
+          <t>482153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>946079</t>
+          <t>950140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174335</t>
+          <t>175196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218608</t>
+          <t>218387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155520</t>
+          <t>155730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186911</t>
+          <t>189236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341537</t>
+          <t>341155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>395846</t>
+          <t>396141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>338865</t>
+          <t>339086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383138</t>
+          <t>382277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>358041</t>
+          <t>355716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389432</t>
+          <t>389222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706579</t>
+          <t>706284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>760888</t>
+          <t>761270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130449</t>
+          <t>128798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160044</t>
+          <t>158720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57443</t>
+          <t>52769</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>210013</t>
+          <t>209073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150166</t>
+          <t>140546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>363310</t>
+          <t>361879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205972</t>
+          <t>207296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235567</t>
+          <t>237218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>397318</t>
+          <t>398258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>549888</t>
+          <t>554562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>610037</t>
+          <t>611468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>823181</t>
+          <t>832801</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77888</t>
+          <t>78350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102705</t>
+          <t>104661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93786</t>
+          <t>93984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119314</t>
+          <t>119358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179593</t>
+          <t>177823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215344</t>
+          <t>215085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175779</t>
+          <t>173823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200596</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296143</t>
+          <t>296099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321671</t>
+          <t>321473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478597</t>
+          <t>478856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514348</t>
+          <t>516118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1597551</t>
+          <t>1598032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2146360</t>
+          <t>2134364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1122807</t>
+          <t>1098223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1496713</t>
+          <t>1489538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2883072</t>
+          <t>2875021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3555898</t>
+          <t>3560702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1303273</t>
+          <t>1315269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1852082</t>
+          <t>1851601</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2143603</t>
+          <t>2150778</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2517509</t>
+          <t>2542093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3534051</t>
+          <t>3529247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4206877</t>
+          <t>4214928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>159910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201264</t>
+          <t>202446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151237</t>
+          <t>151630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191124</t>
+          <t>189028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324829</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>379707</t>
+          <t>380175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218199</t>
+          <t>217017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257626</t>
+          <t>259553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201621</t>
+          <t>203717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241508</t>
+          <t>241115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432501</t>
+          <t>432033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487379</t>
+          <t>490572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173253</t>
+          <t>171313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217698</t>
+          <t>217194</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176075</t>
+          <t>174210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221153</t>
+          <t>218737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359080</t>
+          <t>364169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>424800</t>
+          <t>425817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368257</t>
+          <t>368761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412702</t>
+          <t>414642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337935</t>
+          <t>340351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383013</t>
+          <t>384878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720243</t>
+          <t>719226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785963</t>
+          <t>780874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200080</t>
+          <t>200702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250165</t>
+          <t>248525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179871</t>
+          <t>179826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225097</t>
+          <t>224973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390688</t>
+          <t>391720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457714</t>
+          <t>460815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416120</t>
+          <t>417760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466205</t>
+          <t>465583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435355</t>
+          <t>435479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480581</t>
+          <t>480626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>869022</t>
+          <t>865921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936048</t>
+          <t>935016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148353</t>
+          <t>149156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196035</t>
+          <t>195340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123018</t>
+          <t>124306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166085</t>
+          <t>166504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>285461</t>
+          <t>286045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351215</t>
+          <t>351595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>446765</t>
+          <t>447460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494447</t>
+          <t>493644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479681</t>
+          <t>479262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>522748</t>
+          <t>521460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>937351</t>
+          <t>936971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1003105</t>
+          <t>1002521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104491</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143422</t>
+          <t>146089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79911</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120800</t>
+          <t>117382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196128</t>
+          <t>193828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253387</t>
+          <t>252434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333432</t>
+          <t>330765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372363</t>
+          <t>370692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>375003</t>
+          <t>378421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415892</t>
+          <t>415799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>719270</t>
+          <t>720223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776529</t>
+          <t>778829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96572</t>
+          <t>98231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79230</t>
+          <t>79165</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>124164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167166</t>
+          <t>169414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235806</t>
+          <t>234147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265751</t>
+          <t>264805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>298532</t>
+          <t>298597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>327967</t>
+          <t>328661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542974</t>
+          <t>540726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>587186</t>
+          <t>585976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>37057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>71244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122318</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196563</t>
+          <t>197652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219172</t>
+          <t>220061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328555</t>
+          <t>325244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359898</t>
+          <t>359431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>531168</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>571313</t>
+          <t>571907</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>977737</t>
+          <t>974570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1087075</t>
+          <t>1080195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>877838</t>
+          <t>877364</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>976656</t>
+          <t>988351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1880581</t>
+          <t>1881644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2033723</t>
+          <t>2035801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2293658</t>
+          <t>2300538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2402996</t>
+          <t>2406163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2551448</t>
+          <t>2539753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2650266</t>
+          <t>2650740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4875114</t>
+          <t>4873036</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5028256</t>
+          <t>5027193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>268252</t>
+          <t>268737</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233030</t>
+          <t>235949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297304</t>
+          <t>297316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>185497</t>
+          <t>209999</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>162212</t>
+          <t>184363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207422</t>
+          <t>236025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>453749</t>
+          <t>478735</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>412423</t>
+          <t>436798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>492551</t>
+          <t>515864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131735</t>
+          <t>139056</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102683</t>
+          <t>110477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166957</t>
+          <t>171844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>127703</t>
+          <t>152513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105778</t>
+          <t>126487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150988</t>
+          <t>178149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>259438</t>
+          <t>291570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220636</t>
+          <t>254441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300764</t>
+          <t>333507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>226278</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199506</t>
+          <t>225767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250534</t>
+          <t>282934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>240097</t>
+          <t>270847</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144280</t>
+          <t>248960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286686</t>
+          <t>295150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>466375</t>
+          <t>525820</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>340649</t>
+          <t>488313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>517867</t>
+          <t>563028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>197269</t>
+          <t>221916</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173013</t>
+          <t>193956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224041</t>
+          <t>251123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>270468</t>
+          <t>229245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223879</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366285</t>
+          <t>251132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>467737</t>
+          <t>451162</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416245</t>
+          <t>413954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>593463</t>
+          <t>488669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>281038</t>
+          <t>314114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256654</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306048</t>
+          <t>342855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>278091</t>
+          <t>313014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>259205</t>
+          <t>291811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295379</t>
+          <t>336152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>559129</t>
+          <t>627127</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>529826</t>
+          <t>593017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>592379</t>
+          <t>660768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>255300</t>
+          <t>306723</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230290</t>
+          <t>277982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279684</t>
+          <t>332311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>263674</t>
+          <t>308315</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246386</t>
+          <t>285177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282560</t>
+          <t>329518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>518974</t>
+          <t>615038</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485724</t>
+          <t>581397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548277</t>
+          <t>649148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,102 +4734,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>540461</t>
+          <t>319751</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>393604</t>
+          <t>294348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>740368</t>
+          <t>348354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>42,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>282414</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>260773</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>304310</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>41,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>602165</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>566073</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>634969</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>44,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>264998</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>224137</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>289858</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>31,7%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>805459</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>644694</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1112681</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>50,5%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -4847,102 +4847,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>347325</t>
+          <t>380866</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147418</t>
+          <t>352263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494182</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>57,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>448968</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>427072</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>470609</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>58,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>64,35%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>829834</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>797030</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>865926</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>55,66%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>442050</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>417190</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>482911</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>68,3%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>789375</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>482153</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>950140</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>49,5%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>30,23%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>196324</t>
+          <t>214061</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175196</t>
+          <t>194428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218387</t>
+          <t>238661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>171703</t>
+          <t>191131</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155730</t>
+          <t>173679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>209081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>368027</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341155</t>
+          <t>375321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396141</t>
+          <t>432499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>361149</t>
+          <t>391110</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339086</t>
+          <t>366510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382277</t>
+          <t>410743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>373249</t>
+          <t>414621</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>355716</t>
+          <t>396671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389222</t>
+          <t>432073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>734398</t>
+          <t>805732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706284</t>
+          <t>778425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>761270</t>
+          <t>835603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>162847</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>128798</t>
+          <t>145803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158720</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>135187</t>
+          <t>147740</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52769</t>
+          <t>133820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>209073</t>
+          <t>162484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>279859</t>
+          <t>310586</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140546</t>
+          <t>287658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361879</t>
+          <t>334138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221344</t>
+          <t>242006</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207296</t>
+          <t>225277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237218</t>
+          <t>259050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>472144</t>
+          <t>290338</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>398258</t>
+          <t>275594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>554562</t>
+          <t>304258</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>693488</t>
+          <t>532345</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>611468</t>
+          <t>508793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>832801</t>
+          <t>555273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>90119</t>
+          <t>99902</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>86377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104661</t>
+          <t>113626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>105811</t>
+          <t>115932</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93984</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119358</t>
+          <t>131113</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>195930</t>
+          <t>215834</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177823</t>
+          <t>197703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215085</t>
+          <t>237816</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>188365</t>
+          <t>205729</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173823</t>
+          <t>192005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200134</t>
+          <t>219254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>309646</t>
+          <t>337642</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296099</t>
+          <t>322461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321473</t>
+          <t>351478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>498011</t>
+          <t>543371</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478856</t>
+          <t>521389</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>516118</t>
+          <t>561502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1598032</t>
+          <t>1564810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2134364</t>
+          <t>1698228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1098223</t>
+          <t>1472474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1489538</t>
+          <t>1587964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2875021</t>
+          <t>3077618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3560702</t>
+          <t>3250344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1702489</t>
+          <t>1887409</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1315269</t>
+          <t>1823565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1851601</t>
+          <t>1956983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2258933</t>
+          <t>2181642</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2150778</t>
+          <t>2124754</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2542093</t>
+          <t>2240244</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3961421</t>
+          <t>4069051</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3529247</t>
+          <t>3984167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4214928</t>
+          <t>4156893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
